--- a/public/Dados_copese.xlsx
+++ b/public/Dados_copese.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\sisu-ufpi-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35D78E0A-29F0-4A6C-8116-813FA17838DD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2693AA-4DE2-44BA-865D-A72BF59D9C7B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,8 @@
     <sheet name="convocacoes" sheetId="3" r:id="rId2"/>
     <sheet name="lista_espera" sheetId="4" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">convocacoes!$A$1:$L$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">convocacoes!$A$1:$L$186</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">lista_espera!$A$1:$N$1121</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">vagas!$A$1:$I$59</definedName>
   </definedNames>
@@ -37,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14099" uniqueCount="1615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14418" uniqueCount="1603">
   <si>
     <t>ano_s</t>
   </si>
@@ -4752,39 +4749,21 @@
     <t>2º Chamada da lista de espera</t>
   </si>
   <si>
-    <t xml:space="preserve">HANNA SOARES BAKKE </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.444.003-** </t>
   </si>
   <si>
-    <t xml:space="preserve">HENRIQUE SANCHES NAPOLITANO </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.434.878-** </t>
   </si>
   <si>
-    <t xml:space="preserve">MARIA VITÓRIA COELHO CARVALHO </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.574.023-** </t>
   </si>
   <si>
-    <t xml:space="preserve">HEDVÂNIA DA SILVA SOUSA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.002.033-** </t>
   </si>
   <si>
-    <t xml:space="preserve">GABRIEL CHILAVER NUNES </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.362.778-** </t>
   </si>
   <si>
-    <t xml:space="preserve">LUCAS LINHARES SILVA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.628.936-** </t>
   </si>
   <si>
@@ -4794,72 +4773,39 @@
     <t xml:space="preserve">***.516.023-** </t>
   </si>
   <si>
-    <t xml:space="preserve">HANNAH ARAÚJO SOARES </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.401.823-** </t>
   </si>
   <si>
-    <t xml:space="preserve">MILLA GOUDINHO DA COSTA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.907.153-** </t>
   </si>
   <si>
-    <t xml:space="preserve">BEATRIZ DA COSTA COELHO </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.126.963-** </t>
   </si>
   <si>
     <t>#</t>
   </si>
   <si>
-    <t xml:space="preserve">AURINEIDE ALMEIDA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.756.873-** </t>
   </si>
   <si>
-    <t xml:space="preserve">CARLA KALINE NASCIMENTO DE SOUSA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.928.983-** </t>
   </si>
   <si>
-    <t xml:space="preserve">KAUAN YAGO GOMES DE ANDRADE </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.219.743-** </t>
   </si>
   <si>
-    <t xml:space="preserve">CAUÊ DE OLIVEIRA SABOIA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.090.563-** </t>
   </si>
   <si>
-    <t xml:space="preserve">CRISMEL MOTA ALENCAR BEZERRA </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.511.143-** </t>
   </si>
   <si>
-    <t xml:space="preserve">IGSON ROCHA RIBEIRO </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.058.203-** </t>
   </si>
   <si>
-    <t xml:space="preserve">EROS MELO DA ROCHA NOGUEIRA BARROS </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.240.563-** </t>
   </si>
   <si>
-    <t xml:space="preserve">ENZO MELO DA ROCHA NOGUEIRA BARROS </t>
-  </si>
-  <si>
     <t xml:space="preserve">***.240.553-** </t>
   </si>
   <si>
@@ -4875,24 +4821,46 @@
     <t>Matrícula Deferida</t>
   </si>
   <si>
-    <t>Aguardando Matrícula</t>
-  </si>
-  <si>
     <t>motivo_n_matriculado</t>
   </si>
   <si>
     <t>Trancado</t>
+  </si>
+  <si>
+    <t>3º Lista de espera</t>
+  </si>
+  <si>
+    <t>3º Chamada da lista de espera</t>
+  </si>
+  <si>
+    <t>Não Compareceu</t>
+  </si>
+  <si>
+    <t>Matrícula Indeferida</t>
+  </si>
+  <si>
+    <t>Aguardando matrícula</t>
+  </si>
+  <si>
+    <t>ND</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4971,30 +4939,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5010,2251 +4981,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Candidatos"/>
-      <sheetName val="Planilha1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="2">
-          <cell r="E2" t="str">
-            <v>ALICIA CÂMARA RIBAS</v>
-          </cell>
-          <cell r="G2" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I2" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="E3" t="str">
-            <v>ANA LUÍZA MAGALHÃES SPINDOLA MENESES</v>
-          </cell>
-          <cell r="F3">
-            <v>795.07</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I3" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="E4" t="str">
-            <v>ANA LUIZA SOUSA EVANGELISTA VIEIRA</v>
-          </cell>
-          <cell r="F4">
-            <v>797.27</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="E5" t="str">
-            <v>ANA PAULA DOS SANTOS BARROS</v>
-          </cell>
-          <cell r="G5" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I5" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="E6" t="str">
-            <v>ANDRÉ LUCAS DE SOUZA SILVA</v>
-          </cell>
-          <cell r="F6">
-            <v>693.78</v>
-          </cell>
-          <cell r="G6" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="I6" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7" t="str">
-            <v>ANDRERSON BRITO SAMPAIO</v>
-          </cell>
-          <cell r="G7" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="I7" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="E8" t="str">
-            <v>ARMANDO BRUNO CARVALHO SA</v>
-          </cell>
-          <cell r="G8" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I8" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9" t="str">
-            <v>AUGUSTO ANDRADE DE MORAES NETO</v>
-          </cell>
-          <cell r="F9">
-            <v>800.25</v>
-          </cell>
-          <cell r="G9" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I9" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="E10" t="str">
-            <v>BEATRIZ BARBOSA DA COSTA DE FREITAS PINTO</v>
-          </cell>
-          <cell r="G10" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I10" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="E11" t="str">
-            <v>BRUNO ÂNGELO DUARTE BRAULIO</v>
-          </cell>
-          <cell r="G11" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I11" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="E12" t="str">
-            <v>DANIEL DE SOUZA VICTOR</v>
-          </cell>
-          <cell r="F12">
-            <v>721.62</v>
-          </cell>
-          <cell r="G12" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I12" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="E13" t="str">
-            <v>EDUARDO BREDA ALTOÉ</v>
-          </cell>
-          <cell r="F13">
-            <v>783.27</v>
-          </cell>
-          <cell r="G13" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I13" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="E14" t="str">
-            <v>EDUARDO SÉRGIO BASTOS DE OLIVEIRA</v>
-          </cell>
-          <cell r="F14">
-            <v>726.02</v>
-          </cell>
-          <cell r="G14" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I14" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="E15" t="str">
-            <v>ELIAQUIM JOSE PEREIRA DA SILVA</v>
-          </cell>
-          <cell r="G15" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I15" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="E16" t="str">
-            <v>FELIPE DA SILVA ALBUQUERQUE</v>
-          </cell>
-          <cell r="F16">
-            <v>795.86</v>
-          </cell>
-          <cell r="G16" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I16" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="E17" t="str">
-            <v>GABRIEL CHILAVER NUNES</v>
-          </cell>
-          <cell r="G17" t="str">
-            <v>PPI-1</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="E18" t="str">
-            <v>GILMAN GABRIEL GOMES MENDES JÚNIOR</v>
-          </cell>
-          <cell r="F18">
-            <v>807.2</v>
-          </cell>
-          <cell r="G18" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I18" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="E19" t="str">
-            <v>GLENDALICE DA SILVA RODRIGUES DE SOUSA</v>
-          </cell>
-          <cell r="G19" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I19" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="E20" t="str">
-            <v>GUILHERME ARTHUR FEITOSA ALVES</v>
-          </cell>
-          <cell r="F20">
-            <v>720.59</v>
-          </cell>
-          <cell r="G20" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I20" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="E21" t="str">
-            <v>HANNA SOARES BAKKE</v>
-          </cell>
-          <cell r="G21" t="str">
-            <v>AC</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="E22" t="str">
-            <v>HANNAH ARAÚJO SOARES</v>
-          </cell>
-          <cell r="G22" t="str">
-            <v>PCD-2</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="E23" t="str">
-            <v>HEDVÂNIA DA SILVA SOUSA</v>
-          </cell>
-          <cell r="G23" t="str">
-            <v>PPI-1</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="E24" t="str">
-            <v>HENRIQUE SANCHES NAPOLITANO</v>
-          </cell>
-          <cell r="G24" t="str">
-            <v>AC</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="E25" t="str">
-            <v>ISABELA ALVES DOS PRAZERES</v>
-          </cell>
-          <cell r="F25">
-            <v>740.16</v>
-          </cell>
-          <cell r="G25" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I25" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="E26" t="str">
-            <v>ISABELLA RIBEIRO SALES</v>
-          </cell>
-          <cell r="G26" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I26" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="E27" t="str">
-            <v>ISABELLA SANTIAGO CARVALHO</v>
-          </cell>
-          <cell r="G27" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I27" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="E28" t="str">
-            <v>JEFFERSON XAVIER PAULO</v>
-          </cell>
-          <cell r="F28">
-            <v>783.22</v>
-          </cell>
-          <cell r="G28" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I28" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="E29" t="str">
-            <v>JOALISON ÁLVARO COSTA</v>
-          </cell>
-          <cell r="G29" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I29" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="E30" t="str">
-            <v>JOÃO GABRIEL LOPES LIMA</v>
-          </cell>
-          <cell r="F30">
-            <v>848.11</v>
-          </cell>
-          <cell r="G30" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I30" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="E31" t="str">
-            <v>JOÃO PEDRO MENDES DA SILVA</v>
-          </cell>
-          <cell r="F31">
-            <v>753.55</v>
-          </cell>
-          <cell r="G31" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I31" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="E32" t="str">
-            <v>JOHANN YUASA AZEKA</v>
-          </cell>
-          <cell r="F32">
-            <v>795.54</v>
-          </cell>
-          <cell r="G32" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I32" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="E33" t="str">
-            <v>JÚLIO CÉSAR RIBEIRO LOPES MOTA</v>
-          </cell>
-          <cell r="G33" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I33" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="E34" t="str">
-            <v>JÚLIO EMANOEL EPIFÂNIO PEREIRA</v>
-          </cell>
-          <cell r="F34">
-            <v>726.23</v>
-          </cell>
-          <cell r="G34" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="I34" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="E35" t="str">
-            <v>KAUÃ MENESES CORRÊA</v>
-          </cell>
-          <cell r="F35">
-            <v>829.61</v>
-          </cell>
-          <cell r="G35" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I35" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="E36" t="str">
-            <v>LANNY SOPHIA DOS SANTOS SOUSA</v>
-          </cell>
-          <cell r="F36">
-            <v>739.54</v>
-          </cell>
-          <cell r="G36" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I36" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="E37" t="str">
-            <v>LUCAS ARTHUR DA PAZ DE OLIVEIRA SANTOS</v>
-          </cell>
-          <cell r="G37" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I37" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="E38" t="str">
-            <v>LUCAS GABRIEL CASTRO SOUSA LIMA</v>
-          </cell>
-          <cell r="F38">
-            <v>728.85</v>
-          </cell>
-          <cell r="G38" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I38" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="E39" t="str">
-            <v>LUCAS GABRIEL DE ARAUJO FLORENTINO</v>
-          </cell>
-          <cell r="F39">
-            <v>745.98</v>
-          </cell>
-          <cell r="G39" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I39" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="E40" t="str">
-            <v>LUCAS LINHARES SILVA</v>
-          </cell>
-          <cell r="G40" t="str">
-            <v>PPI-1</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="E41" t="str">
-            <v>LUNA EDUARDA ALMEIDA CRUZ</v>
-          </cell>
-          <cell r="F41">
-            <v>731.62</v>
-          </cell>
-          <cell r="G41" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="I41" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="E42" t="str">
-            <v>LUYARA XAVIER DE ANDRADE</v>
-          </cell>
-          <cell r="F42">
-            <v>744.05</v>
-          </cell>
-          <cell r="G42" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I42" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="E43" t="str">
-            <v>MANOEL ALVES DE CASTRO NETO</v>
-          </cell>
-          <cell r="F43">
-            <v>742.54</v>
-          </cell>
-          <cell r="G43" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I43" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="E44" t="str">
-            <v>MANUEL ANTONY ANDRADE GUARITA</v>
-          </cell>
-          <cell r="F44">
-            <v>804.39</v>
-          </cell>
-          <cell r="G44" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I44" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="E45" t="str">
-            <v>MARIA CLARA MARTINS SOUSA</v>
-          </cell>
-          <cell r="G45" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I45" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="E46" t="str">
-            <v>MARIA EDUARDA VIEIRA DE BRITO</v>
-          </cell>
-          <cell r="G46" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I46" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="E47" t="str">
-            <v>MARIA FERNANDA CARDOSO SOARES</v>
-          </cell>
-          <cell r="G47" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I47" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="E48" t="str">
-            <v>MARIA FERNANDA LIMA ANDRADE</v>
-          </cell>
-          <cell r="F48">
-            <v>800.33</v>
-          </cell>
-          <cell r="G48" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I48" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="E49" t="str">
-            <v>MARIA VITÓRIA COELHO CARVALHO</v>
-          </cell>
-          <cell r="G49" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I49" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="E50" t="str">
-            <v>MARYANNA PINHEIRO PACHECO SILVA</v>
-          </cell>
-          <cell r="G50" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I50" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="E51" t="str">
-            <v>MILEIDE MARIA ALMEIDA GOMES</v>
-          </cell>
-          <cell r="F51">
-            <v>723.38</v>
-          </cell>
-          <cell r="G51" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I51" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="E52" t="str">
-            <v>NALANDA VITÓRIA SOUZA PEREIRA</v>
-          </cell>
-          <cell r="G52" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I52" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="E53" t="str">
-            <v>RAFAEL SARAIVA LIMA SILVA</v>
-          </cell>
-          <cell r="G53" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I53" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="E54" t="str">
-            <v>RAY NOGUEIRA LEAL</v>
-          </cell>
-          <cell r="G54" t="str">
-            <v>PPI-1</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="E55" t="str">
-            <v>REBECA SANTANA DE OLIVEIRA</v>
-          </cell>
-          <cell r="G55" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I55" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="E56" t="str">
-            <v>REMILLY PACHECO PINHEIRO PIMENTEL</v>
-          </cell>
-          <cell r="F56">
-            <v>729.12</v>
-          </cell>
-          <cell r="G56" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I56" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="E57" t="str">
-            <v>RICK DE SIQUEIRA FURTADO</v>
-          </cell>
-          <cell r="F57">
-            <v>726.82</v>
-          </cell>
-          <cell r="G57" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I57" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="E58" t="str">
-            <v>SAMYA AMYLEE ALMEIDA INACIO</v>
-          </cell>
-          <cell r="G58" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="I58" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="E59" t="str">
-            <v>THAWERTY BROLIN VIEIRA NASCIMENTO</v>
-          </cell>
-          <cell r="F59">
-            <v>800.41</v>
-          </cell>
-          <cell r="G59" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I59" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="E60" t="str">
-            <v>VITOR VIANA SOARES MARQUES</v>
-          </cell>
-          <cell r="G60" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I60" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="E61" t="str">
-            <v>WALBER VELOSO SANTOS LEAL</v>
-          </cell>
-          <cell r="F61">
-            <v>803.47</v>
-          </cell>
-          <cell r="G61" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I61" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="E62" t="str">
-            <v>ALLAN ERIC BARROS DA SILVA</v>
-          </cell>
-          <cell r="F62">
-            <v>572.36</v>
-          </cell>
-          <cell r="G62" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="H62" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I62" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="E63" t="str">
-            <v>ANTONIO WELISON BANDEIRA DA SILVA</v>
-          </cell>
-          <cell r="F63">
-            <v>613.22</v>
-          </cell>
-          <cell r="G63" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I63" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="E64" t="str">
-            <v>AQUILES LIMA EVARISTO</v>
-          </cell>
-          <cell r="G64" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I64" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="E65" t="str">
-            <v>CARLOS SAMUEL FREITAS BARBOSA</v>
-          </cell>
-          <cell r="F65">
-            <v>609.86</v>
-          </cell>
-          <cell r="G65" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I65" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="E66" t="str">
-            <v>CAUA FIGUEIREDO DE OLIVEIRA</v>
-          </cell>
-          <cell r="F66">
-            <v>693.41</v>
-          </cell>
-          <cell r="G66" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I66" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="E67" t="str">
-            <v>CAUÊ DE OLIVEIRA SABOIA</v>
-          </cell>
-          <cell r="G67" t="str">
-            <v>AC</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="E68" t="str">
-            <v>CRISMEL MOTA ALENCAR BEZERRA</v>
-          </cell>
-          <cell r="G68" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="H68" t="str">
-            <v>EP-2</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="E69" t="str">
-            <v>DENILSON RIBEIRO LOPES</v>
-          </cell>
-          <cell r="F69">
-            <v>638.63</v>
-          </cell>
-          <cell r="G69" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I69" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="E70" t="str">
-            <v>EDMAR DE ALMEIDA NETO</v>
-          </cell>
-          <cell r="F70">
-            <v>708.66</v>
-          </cell>
-          <cell r="G70" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I70" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="E71" t="str">
-            <v>ELISA VITÓRIA FERNANDES DA MOTA</v>
-          </cell>
-          <cell r="F71">
-            <v>671.59</v>
-          </cell>
-          <cell r="G71" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I71" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="E72" t="str">
-            <v>ENZO DA SILVA ARAÚJO MONTEIRO</v>
-          </cell>
-          <cell r="F72">
-            <v>718.25</v>
-          </cell>
-          <cell r="G72" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I72" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="E73" t="str">
-            <v>ENZO MELO DA ROCHA NOGUEIRA BARROS</v>
-          </cell>
-          <cell r="G73" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="H73" t="str">
-            <v>EP-2</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="E74" t="str">
-            <v>EROS MELO DA ROCHA NOGUEIRA BARROS</v>
-          </cell>
-          <cell r="G74" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="H74" t="str">
-            <v>EP-2</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="E75" t="str">
-            <v>FÁBIO LUIZ FERREIRA DA COSTA JÚNIOR</v>
-          </cell>
-          <cell r="G75" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I75" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="E76" t="str">
-            <v>FABRÍCIO LOPES DOS SANTOS</v>
-          </cell>
-          <cell r="F76">
-            <v>724.46</v>
-          </cell>
-          <cell r="G76" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I76" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="E77" t="str">
-            <v>GUILHERME JOSÉ COELHO AMORIM</v>
-          </cell>
-          <cell r="F77">
-            <v>731.68</v>
-          </cell>
-          <cell r="G77" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I77" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="E78" t="str">
-            <v>GUILHERME MOTA BEZERRA</v>
-          </cell>
-          <cell r="G78" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="H78" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I78" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="E79" t="str">
-            <v>GUSTAVO HENRIQUE CASTRO MARTINS</v>
-          </cell>
-          <cell r="F79">
-            <v>668.94</v>
-          </cell>
-          <cell r="G79" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I79" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="E80" t="str">
-            <v>HAYLA FRANCISCA DE NAZARETH E SILVA</v>
-          </cell>
-          <cell r="F80">
-            <v>534.5</v>
-          </cell>
-          <cell r="G80" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I80" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="E81" t="str">
-            <v>IGSON ROCHA RIBEIRO</v>
-          </cell>
-          <cell r="G81" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="H81" t="str">
-            <v>EP-2</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="E82" t="str">
-            <v>IKARO GABRIEL MARQUES DOS SANTOS</v>
-          </cell>
-          <cell r="F82">
-            <v>585.30999999999995</v>
-          </cell>
-          <cell r="G82" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I82" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="E83" t="str">
-            <v>JOÃO MARCELO DA SILVA ROCHA</v>
-          </cell>
-          <cell r="G83" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I83" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="E84" t="str">
-            <v>JOÃO VICENTE DUARTE OLIVEIRA</v>
-          </cell>
-          <cell r="F84">
-            <v>708.79</v>
-          </cell>
-          <cell r="G84" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I84" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="E85" t="str">
-            <v>JOAO VITO LEITE RODRIGUES DE CARVALHO</v>
-          </cell>
-          <cell r="F85">
-            <v>722.43</v>
-          </cell>
-          <cell r="G85" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I85" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="E86" t="str">
-            <v>JOSÉ HAMILTON SANTANA NOGUEIRA</v>
-          </cell>
-          <cell r="F86">
-            <v>568.49</v>
-          </cell>
-          <cell r="G86" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I86" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="E87" t="str">
-            <v>KAIO RÔMULO DE OLIVEIRA LOPES</v>
-          </cell>
-          <cell r="F87">
-            <v>599.89</v>
-          </cell>
-          <cell r="G87" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I87" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="E88" t="str">
-            <v>KÁSSIO CARDOSO ROCHA</v>
-          </cell>
-          <cell r="F88">
-            <v>636.5</v>
-          </cell>
-          <cell r="G88" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I88" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="E89" t="str">
-            <v>KAYLA FERNANDA PEREIRA ALMEIDA</v>
-          </cell>
-          <cell r="F89">
-            <v>645.09</v>
-          </cell>
-          <cell r="G89" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I89" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="E90" t="str">
-            <v>KAYRA TALESSA LUZ SILVA</v>
-          </cell>
-          <cell r="F90">
-            <v>616.08000000000004</v>
-          </cell>
-          <cell r="G90" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I90" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="E91" t="str">
-            <v>LARA ANDRADE</v>
-          </cell>
-          <cell r="F91">
-            <v>698.47</v>
-          </cell>
-          <cell r="G91" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I91" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="E92" t="str">
-            <v>LEANDRO OLIVEIRA LOPES</v>
-          </cell>
-          <cell r="F92">
-            <v>587.08000000000004</v>
-          </cell>
-          <cell r="G92" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I92" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="E93" t="str">
-            <v>LUAN BARBOSA FONTES</v>
-          </cell>
-          <cell r="F93">
-            <v>652.83000000000004</v>
-          </cell>
-          <cell r="G93" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I93" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="E94" t="str">
-            <v>LUCAS DA SILVA OLIVEIRA</v>
-          </cell>
-          <cell r="G94" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I94" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="E95" t="str">
-            <v>LUCAS GABRIEL DA SILVA ARAÚJO</v>
-          </cell>
-          <cell r="F95">
-            <v>597.07000000000005</v>
-          </cell>
-          <cell r="G95" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I95" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="E96" t="str">
-            <v>LUIZ EDUARDO FREITAS DE CARVALHO</v>
-          </cell>
-          <cell r="G96" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="H96" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I96" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="E97" t="str">
-            <v>LUIZ EDUARDO PITOMBEIRA MENDES SANTOS E SILVA</v>
-          </cell>
-          <cell r="F97">
-            <v>721.65</v>
-          </cell>
-          <cell r="G97" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I97" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="E98" t="str">
-            <v>MARCELO HENRIQUE DOS SANTOS SILVA</v>
-          </cell>
-          <cell r="F98">
-            <v>568.89</v>
-          </cell>
-          <cell r="G98" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="H98" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I98" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="E99" t="str">
-            <v>MARCOS VINICIUS DE CARVALHO BATISTA</v>
-          </cell>
-          <cell r="F99">
-            <v>578.16</v>
-          </cell>
-          <cell r="G99" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="H99" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I99" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="E100" t="str">
-            <v>MARCUS KAUÃ MONTEIRO RABÊLO</v>
-          </cell>
-          <cell r="F100">
-            <v>713.26</v>
-          </cell>
-          <cell r="G100" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I100" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="E101" t="str">
-            <v>MARIA EDUARDA BARBOSA BRITO</v>
-          </cell>
-          <cell r="F101">
-            <v>700.31</v>
-          </cell>
-          <cell r="G101" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I101" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="E102" t="str">
-            <v>MATEUS GOMES RODRIGUES ANDRADE</v>
-          </cell>
-          <cell r="F102">
-            <v>683.71</v>
-          </cell>
-          <cell r="G102" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I102" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="E103" t="str">
-            <v>MÁXIMUS SAMUEL MENDES DE JESUS</v>
-          </cell>
-          <cell r="F103">
-            <v>707.63</v>
-          </cell>
-          <cell r="G103" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I103" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="E104" t="str">
-            <v>MURILO COELHO DA SILVA</v>
-          </cell>
-          <cell r="F104">
-            <v>737.06</v>
-          </cell>
-          <cell r="G104" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I104" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="E105" t="str">
-            <v>PALOMA MARIA PEREIRA DOS SANTOS</v>
-          </cell>
-          <cell r="G105" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I105" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="E106" t="str">
-            <v>PEDRO HENRIQUE VELOSO BESERRA DA SILVA</v>
-          </cell>
-          <cell r="G106" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I106" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="E107" t="str">
-            <v>RAFAEL CARVALHO DOS SANTOS</v>
-          </cell>
-          <cell r="F107">
-            <v>687.01</v>
-          </cell>
-          <cell r="G107" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I107" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="E108" t="str">
-            <v>RAFAEL VIEIRA VALENÇA</v>
-          </cell>
-          <cell r="F108">
-            <v>732.98</v>
-          </cell>
-          <cell r="G108" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I108" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="E109" t="str">
-            <v>SALATIEL RODRIGUES DA CONCEIÇÃO</v>
-          </cell>
-          <cell r="G109" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="H109" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I109" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="E110" t="str">
-            <v>SILVANA MENESES DAMASCENO</v>
-          </cell>
-          <cell r="G110" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I110" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="E111" t="str">
-            <v>SOPHIA ALVES MINEIRO</v>
-          </cell>
-          <cell r="G111" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="H111" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I111" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="E112" t="str">
-            <v>SWELEN NAYANE PIRES DE SA</v>
-          </cell>
-          <cell r="G112" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="H112" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I112" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="E113" t="str">
-            <v>VINÍCIUS SOARES DA FONSECA</v>
-          </cell>
-          <cell r="F113">
-            <v>710.15</v>
-          </cell>
-          <cell r="G113" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I113" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="E114" t="str">
-            <v>YANNA CABEDO CRONEMBERGER</v>
-          </cell>
-          <cell r="F114">
-            <v>603.99</v>
-          </cell>
-          <cell r="G114" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I114" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="E115" t="str">
-            <v>YASMIM BEATRIZ BARROS DE ARAUJO</v>
-          </cell>
-          <cell r="G115" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="H115" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I115" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="E116" t="str">
-            <v>ALEXANDRO MOURA SOARES</v>
-          </cell>
-          <cell r="G116" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="I116" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="E117" t="str">
-            <v>AMANDA AZEVEDO DA SILVA</v>
-          </cell>
-          <cell r="F117">
-            <v>670.41</v>
-          </cell>
-          <cell r="G117" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I117" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="E118" t="str">
-            <v>ANA CLÁUDIA DE MENESES VIANA</v>
-          </cell>
-          <cell r="F118">
-            <v>711.39</v>
-          </cell>
-          <cell r="G118" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I118" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="E119" t="str">
-            <v>ANA LUISA ARAÚJO PORTELA</v>
-          </cell>
-          <cell r="F119">
-            <v>631.66999999999996</v>
-          </cell>
-          <cell r="G119" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I119" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="E120" t="str">
-            <v>ANNA CAMILLA DA ROCHA MARCAL BEZERRA</v>
-          </cell>
-          <cell r="G120" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I120" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="121">
-          <cell r="E121" t="str">
-            <v>ANTÔNIA CLARA ALVES DE OLIVEIRA</v>
-          </cell>
-          <cell r="F121">
-            <v>637.04</v>
-          </cell>
-          <cell r="G121" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I121" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="122">
-          <cell r="E122" t="str">
-            <v>ARTHUR ERIK DE MESQUITA SOUSA</v>
-          </cell>
-          <cell r="F122">
-            <v>634.82000000000005</v>
-          </cell>
-          <cell r="G122" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I122" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="123">
-          <cell r="E123" t="str">
-            <v>ARTHUR HENRIQUE GALVÃO DA SILVA</v>
-          </cell>
-          <cell r="F123">
-            <v>627.89</v>
-          </cell>
-          <cell r="G123" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I123" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="124">
-          <cell r="E124" t="str">
-            <v>ARTHUR HENRIQUE MONTURIL SILVA COSTA</v>
-          </cell>
-          <cell r="F124">
-            <v>696.12</v>
-          </cell>
-          <cell r="G124" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I124" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="125">
-          <cell r="E125" t="str">
-            <v>AURINEIDE ALMEIDA</v>
-          </cell>
-          <cell r="G125" t="str">
-            <v>PCD-1</v>
-          </cell>
-        </row>
-        <row r="126">
-          <cell r="E126" t="str">
-            <v>BEATRIZ DA COSTA COELHO</v>
-          </cell>
-          <cell r="G126" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="H126" t="str">
-            <v>PPI-1</v>
-          </cell>
-        </row>
-        <row r="127">
-          <cell r="E127" t="str">
-            <v>BEATRIZ OLIVEIRA CARVALHO</v>
-          </cell>
-          <cell r="F127">
-            <v>708.99</v>
-          </cell>
-          <cell r="G127" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I127" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="128">
-          <cell r="E128" t="str">
-            <v>BIANCA MARIA DA SILVA PEREIRA</v>
-          </cell>
-          <cell r="F128">
-            <v>701.2</v>
-          </cell>
-          <cell r="G128" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I128" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="129">
-          <cell r="E129" t="str">
-            <v>CARLA KALINE NASCIMENTO DE SOUSA</v>
-          </cell>
-          <cell r="G129" t="str">
-            <v>PCD-2</v>
-          </cell>
-        </row>
-        <row r="130">
-          <cell r="E130" t="str">
-            <v>CARLOS EDUARDO DE MOURA SILVA</v>
-          </cell>
-          <cell r="F130">
-            <v>612.94000000000005</v>
-          </cell>
-          <cell r="G130" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I130" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="131">
-          <cell r="E131" t="str">
-            <v>DAER SHALAAN VASCONCELOS PIAUILINO</v>
-          </cell>
-          <cell r="F131">
-            <v>692.83</v>
-          </cell>
-          <cell r="G131" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I131" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="132">
-          <cell r="E132" t="str">
-            <v>DANIELLA MARIA OLIVEIRA ALBUQUERQUE DE SOUSA</v>
-          </cell>
-          <cell r="F132">
-            <v>695.39</v>
-          </cell>
-          <cell r="G132" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I132" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="133">
-          <cell r="E133" t="str">
-            <v>DÉBORA MARIA DA SILVA</v>
-          </cell>
-          <cell r="F133">
-            <v>629.01</v>
-          </cell>
-          <cell r="G133" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I133" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="134">
-          <cell r="E134" t="str">
-            <v>DORA RIBEIRO FARIAS</v>
-          </cell>
-          <cell r="F134">
-            <v>695.59</v>
-          </cell>
-          <cell r="G134" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I134" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="135">
-          <cell r="E135" t="str">
-            <v>EMILLE MABELLE LIMA DE ARAUJO OLIVEIRA</v>
-          </cell>
-          <cell r="G135" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I135" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="136">
-          <cell r="E136" t="str">
-            <v>GIOVANNA VITÓRIA LEAL DE BRITO</v>
-          </cell>
-          <cell r="F136">
-            <v>688.38</v>
-          </cell>
-          <cell r="G136" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I136" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="137">
-          <cell r="E137" t="str">
-            <v>HANNA BEATRIZ COSTA SARAIVA ALVES LEAL</v>
-          </cell>
-          <cell r="F137">
-            <v>701.02</v>
-          </cell>
-          <cell r="G137" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I137" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="138">
-          <cell r="E138" t="str">
-            <v>HENRICO GABRIEL SOUSA FERREIRA</v>
-          </cell>
-          <cell r="G138" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I138" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="139">
-          <cell r="E139" t="str">
-            <v>HENZO FREDERICO VIEIRA SILVA</v>
-          </cell>
-          <cell r="F139">
-            <v>694.54</v>
-          </cell>
-          <cell r="G139" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I139" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="140">
-          <cell r="E140" t="str">
-            <v>HERICK JOSÉ MATIAS DA SILVA</v>
-          </cell>
-          <cell r="F140">
-            <v>568.19000000000005</v>
-          </cell>
-          <cell r="G140" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="I140" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="141">
-          <cell r="E141" t="str">
-            <v>ISABELE DIAS CAVALCANTE</v>
-          </cell>
-          <cell r="F141">
-            <v>698.43</v>
-          </cell>
-          <cell r="G141" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I141" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="142">
-          <cell r="E142" t="str">
-            <v>JOÃO EMANOEL DE SOUZA SILVA</v>
-          </cell>
-          <cell r="F142">
-            <v>612.41999999999996</v>
-          </cell>
-          <cell r="G142" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I142" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="143">
-          <cell r="E143" t="str">
-            <v>JOÃO MATEUS FARIAS VIANA</v>
-          </cell>
-          <cell r="F143">
-            <v>631.52</v>
-          </cell>
-          <cell r="G143" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I143" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="144">
-          <cell r="E144" t="str">
-            <v>JOÃO PAULO NUNES MAZZA</v>
-          </cell>
-          <cell r="F144">
-            <v>729.45</v>
-          </cell>
-          <cell r="G144" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I144" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="145">
-          <cell r="E145" t="str">
-            <v>JÚLIA FERNANDA CASTRO TEIXEIRA COSTA</v>
-          </cell>
-          <cell r="F145">
-            <v>705.05</v>
-          </cell>
-          <cell r="G145" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I145" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="146">
-          <cell r="E146" t="str">
-            <v>JÚLIA IRAÍDE ALVES SILVA</v>
-          </cell>
-          <cell r="G146" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I146" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="147">
-          <cell r="E147" t="str">
-            <v>JULIANA DE SOUSA DA SILVA</v>
-          </cell>
-          <cell r="F147">
-            <v>647.98</v>
-          </cell>
-          <cell r="G147" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I147" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="148">
-          <cell r="E148" t="str">
-            <v>JULIANA MARIA SANTOS DE ALBUQUERQUE</v>
-          </cell>
-          <cell r="F148">
-            <v>701.08</v>
-          </cell>
-          <cell r="G148" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I148" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="149">
-          <cell r="E149" t="str">
-            <v>KAUAN YAGO GOMES DE ANDRADE</v>
-          </cell>
-          <cell r="G149" t="str">
-            <v>EP-2</v>
-          </cell>
-        </row>
-        <row r="150">
-          <cell r="E150" t="str">
-            <v>KAYLAN ANDRADE DE CASTRO</v>
-          </cell>
-          <cell r="G150" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I150" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="151">
-          <cell r="E151" t="str">
-            <v>KESYA MYNELLY LOPES CUNHA</v>
-          </cell>
-          <cell r="F151">
-            <v>663.92</v>
-          </cell>
-          <cell r="G151" t="str">
-            <v>EP-1</v>
-          </cell>
-          <cell r="I151" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="152">
-          <cell r="E152" t="str">
-            <v>KEYLA MARA DE SOUSA BASTOS</v>
-          </cell>
-          <cell r="G152" t="str">
-            <v>Q-1</v>
-          </cell>
-          <cell r="I152" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="153">
-          <cell r="E153" t="str">
-            <v>LANNA STHEFANY CONCEIÇÃO DE SOUSA</v>
-          </cell>
-          <cell r="F153">
-            <v>662.14</v>
-          </cell>
-          <cell r="G153" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I153" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="154">
-          <cell r="E154" t="str">
-            <v>LEILIANE NAYARA ALVES DA SILVA</v>
-          </cell>
-          <cell r="F154">
-            <v>659.54</v>
-          </cell>
-          <cell r="G154" t="str">
-            <v>PCD-1</v>
-          </cell>
-          <cell r="I154" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="155">
-          <cell r="E155" t="str">
-            <v>LETÍCIA CAVALCANTE BEZERRA</v>
-          </cell>
-          <cell r="F155">
-            <v>723.46</v>
-          </cell>
-          <cell r="G155" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I155" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="156">
-          <cell r="E156" t="str">
-            <v>LETÍCIA HOLANDA FURTADO</v>
-          </cell>
-          <cell r="F156">
-            <v>712.84</v>
-          </cell>
-          <cell r="G156" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I156" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="157">
-          <cell r="E157" t="str">
-            <v>LUANA HELOÁ LELES DE QUEIROZ</v>
-          </cell>
-          <cell r="F157">
-            <v>627.58000000000004</v>
-          </cell>
-          <cell r="G157" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="H157" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I157" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="158">
-          <cell r="E158" t="str">
-            <v>MARIA CLARA DE SOUSA DE ARAUJO</v>
-          </cell>
-          <cell r="F158">
-            <v>632.54999999999995</v>
-          </cell>
-          <cell r="G158" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I158" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="159">
-          <cell r="E159" t="str">
-            <v>MARIA CLARA DIONE CARVALHO ROCHA</v>
-          </cell>
-          <cell r="G159" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I159" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="160">
-          <cell r="E160" t="str">
-            <v>MARIA EDUARDA DOS SANTOS ROSA LIMA</v>
-          </cell>
-          <cell r="G160" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I160" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="161">
-          <cell r="E161" t="str">
-            <v>MARIA GABRIELY DE ALMEIDA VIEIRA</v>
-          </cell>
-          <cell r="G161" t="str">
-            <v>PCD-2</v>
-          </cell>
-          <cell r="I161" t="str">
-            <v>Matrícula Indeferida</v>
-          </cell>
-        </row>
-        <row r="162">
-          <cell r="E162" t="str">
-            <v>MARIA LUIZA ROCHA E SILVA</v>
-          </cell>
-          <cell r="F162">
-            <v>692.15</v>
-          </cell>
-          <cell r="G162" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I162" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="163">
-          <cell r="E163" t="str">
-            <v>MARIA LUIZA SORIANO DOS ANJOS</v>
-          </cell>
-          <cell r="G163" t="str">
-            <v>EP-2</v>
-          </cell>
-          <cell r="I163" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="164">
-          <cell r="E164" t="str">
-            <v>MARIANA MENDES GARCIA</v>
-          </cell>
-          <cell r="F164">
-            <v>709.66</v>
-          </cell>
-          <cell r="G164" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I164" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="165">
-          <cell r="E165" t="str">
-            <v>MARIANNY DA SILVA PEREIRA</v>
-          </cell>
-          <cell r="F165">
-            <v>632.53</v>
-          </cell>
-          <cell r="G165" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I165" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="166">
-          <cell r="E166" t="str">
-            <v>MARINA LIMA CRUZIO NUNES</v>
-          </cell>
-          <cell r="G166" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I166" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="167">
-          <cell r="E167" t="str">
-            <v>MILA PINHEIRO COSTA</v>
-          </cell>
-          <cell r="F167">
-            <v>698.63</v>
-          </cell>
-          <cell r="G167" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I167" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="168">
-          <cell r="E168" t="str">
-            <v>MILLA GOUDINHO DA COSTA</v>
-          </cell>
-          <cell r="G168" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I168" t="str">
-            <v>Não Compareceu</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="E169" t="str">
-            <v>MILLENA FLORIZA NEVES GUIMARAES</v>
-          </cell>
-          <cell r="G169" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I169" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="170">
-          <cell r="E170" t="str">
-            <v>MOISÉS DOS SANTOS MORAIS</v>
-          </cell>
-          <cell r="G170" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I170" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="E171" t="str">
-            <v>PALOMA BACELAR DOS SANTOS</v>
-          </cell>
-          <cell r="G171" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I171" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="E172" t="str">
-            <v>PEDRO GABRIEL TEIXEIRA RODRIGUES MINEIRO</v>
-          </cell>
-          <cell r="F172">
-            <v>697.45</v>
-          </cell>
-          <cell r="G172" t="str">
-            <v>AC</v>
-          </cell>
-          <cell r="I172" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="173">
-          <cell r="E173" t="str">
-            <v>STEFFANE RODRIGUES DE SOUSA</v>
-          </cell>
-          <cell r="F173">
-            <v>645.62</v>
-          </cell>
-          <cell r="G173" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I173" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="174">
-          <cell r="E174" t="str">
-            <v>THAYANNE GOMES SAMPAIO</v>
-          </cell>
-          <cell r="F174">
-            <v>605.05999999999995</v>
-          </cell>
-          <cell r="G174" t="str">
-            <v>PPI-2</v>
-          </cell>
-          <cell r="I174" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-        <row r="175">
-          <cell r="E175" t="str">
-            <v>THIAGO RYKELM SILVA QUIXABA</v>
-          </cell>
-          <cell r="F175">
-            <v>632.89</v>
-          </cell>
-          <cell r="G175" t="str">
-            <v>PPI-1</v>
-          </cell>
-          <cell r="I175" t="str">
-            <v>Matrícula Deferida</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7533,7 +5259,7 @@
         <v>14</v>
       </c>
       <c r="I2" s="2">
-        <f t="shared" ref="I2:I59" si="0">G2-H2</f>
+        <f t="shared" ref="I2:I65" si="0">G2-H2</f>
         <v>3</v>
       </c>
     </row>
@@ -9150,11 +6876,11 @@
   convocacoes!E:E, F47,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" s="2">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9228,11 +6954,11 @@
   convocacoes!E:E, F49,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I49" s="2">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9264,11 +6990,11 @@
   convocacoes!E:E, F50,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9340,11 +7066,11 @@
   convocacoes!E:E, F52,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9530,11 +7256,11 @@
   convocacoes!E:E, F57,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -9615,27 +7341,377 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A60,
+  convocacoes!B:B, C60,
+  convocacoes!E:E, F60,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I60" s="2">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A61,
+  convocacoes!B:B, C61,
+  convocacoes!E:E, F61,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" t="s">
+        <v>31</v>
+      </c>
+      <c r="F62" t="s">
+        <v>37</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A62,
+  convocacoes!B:B, C62,
+  convocacoes!E:E, F62,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" t="s">
+        <v>210</v>
+      </c>
+      <c r="E63" t="s">
+        <v>108</v>
+      </c>
+      <c r="F63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A63,
+  convocacoes!B:B, C63,
+  convocacoes!E:E, F63,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="s">
+        <v>106</v>
+      </c>
+      <c r="D64" t="s">
+        <v>210</v>
+      </c>
+      <c r="E64" t="s">
+        <v>108</v>
+      </c>
+      <c r="F64" t="s">
+        <v>59</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A64,
+  convocacoes!B:B, C64,
+  convocacoes!E:E, F64,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="s">
+        <v>106</v>
+      </c>
+      <c r="D65" t="s">
+        <v>210</v>
+      </c>
+      <c r="E65" t="s">
+        <v>108</v>
+      </c>
+      <c r="F65" t="s">
+        <v>41</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A65,
+  convocacoes!B:B, C65,
+  convocacoes!E:E, F65,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I65" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>24</v>
+      </c>
+      <c r="F66" t="s">
+        <v>25</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A66,
+  convocacoes!B:B, C66,
+  convocacoes!E:E, F66,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="2">
+        <f t="shared" ref="I66:I69" si="8">G66-H66</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" t="s">
+        <v>51</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A67,
+  convocacoes!B:B, C67,
+  convocacoes!E:E, F67,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" t="s">
+        <v>54</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A68,
+  convocacoes!B:B, C68,
+  convocacoes!E:E, F68,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I68" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="9" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" t="s">
+        <v>41</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69" s="8">
+        <f>COUNTIFS(
+  convocacoes!A:A, A69,
+  convocacoes!B:B, C69,
+  convocacoes!E:E, F69,
+  convocacoes!I:I, 1
+)</f>
+        <v>0</v>
+      </c>
+      <c r="I69" s="2">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="78" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="79" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="80" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10552,6 +8628,7 @@
     <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:I59" xr:uid="{757EA66F-DC97-48A0-A498-5FBE3B3AA156}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -10559,7 +8636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L175"/>
+  <dimension ref="A1:L186"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -10571,7 +8648,9 @@
     <col min="7" max="7" width="39.44140625" customWidth="1"/>
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" customWidth="1"/>
-    <col min="10" max="25" width="8.6640625" customWidth="1"/>
+    <col min="10" max="11" width="8.6640625" customWidth="1"/>
+    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10609,7 +8688,7 @@
         <v>21</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>1613</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10643,9 +8722,8 @@
       <c r="J2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L2" t="str">
-        <f>VLOOKUP(G2,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L2" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10668,7 +8746,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>1609</v>
+        <v>1592</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>56</v>
@@ -10679,9 +8757,8 @@
       <c r="J3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L3" t="str">
-        <f>VLOOKUP(G3,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L3" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10715,9 +8792,8 @@
       <c r="J4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L4" t="str">
-        <f>VLOOKUP(G4,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L4" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10751,9 +8827,8 @@
       <c r="J5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L5" t="str">
-        <f>VLOOKUP(G5,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L5" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10787,9 +8862,8 @@
       <c r="J6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L6" t="str">
-        <f>VLOOKUP(G6,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L6" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10823,9 +8897,8 @@
       <c r="J7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L7" t="str">
-        <f>VLOOKUP(G7,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L7" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10859,9 +8932,8 @@
       <c r="J8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L8" t="str">
-        <f>VLOOKUP(G8,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L8" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10895,9 +8967,8 @@
       <c r="J9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L9" t="str">
-        <f>VLOOKUP(G9,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L9" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10931,9 +9002,8 @@
       <c r="J10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L10" t="str">
-        <f>VLOOKUP(G10,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L10" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -10967,9 +9037,8 @@
       <c r="J11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L11" t="str">
-        <f>VLOOKUP(G11,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L11" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11003,9 +9072,8 @@
       <c r="J12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L12" t="str">
-        <f>VLOOKUP(G12,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L12" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11039,9 +9107,8 @@
       <c r="J13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L13" t="str">
-        <f>VLOOKUP(G13,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L13" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11075,9 +9142,8 @@
       <c r="J14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L14" t="str">
-        <f>VLOOKUP(G14,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L14" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11111,9 +9177,8 @@
       <c r="J15" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L15" t="str">
-        <f>VLOOKUP(G15,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L15" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11147,9 +9212,8 @@
       <c r="J16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L16" t="str">
-        <f>VLOOKUP(G16,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L16" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11183,9 +9247,8 @@
       <c r="J17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L17" t="str">
-        <f>VLOOKUP(G17,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L17" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11219,9 +9282,8 @@
       <c r="J18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L18" t="str">
-        <f>VLOOKUP(G18,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L18" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11255,9 +9317,8 @@
       <c r="J19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L19" t="str">
-        <f>VLOOKUP(G19,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L19" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11291,9 +9352,8 @@
       <c r="J20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L20" t="str">
-        <f>VLOOKUP(G20,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L20" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11327,9 +9387,8 @@
       <c r="J21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L21" t="str">
-        <f>VLOOKUP(G21,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L21" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11363,9 +9422,8 @@
       <c r="J22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L22" t="str">
-        <f>VLOOKUP(G22,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L22" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11399,9 +9457,8 @@
       <c r="J23" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L23" t="str">
-        <f>VLOOKUP(G23,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L23" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11435,9 +9492,8 @@
       <c r="J24" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L24" t="str">
-        <f>VLOOKUP(G24,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L24" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11471,9 +9527,8 @@
       <c r="J25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L25" t="str">
-        <f>VLOOKUP(G25,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L25" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11507,9 +9562,8 @@
       <c r="J26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L26" t="str">
-        <f>VLOOKUP(G26,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L26" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11543,9 +9597,8 @@
       <c r="J27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L27" t="str">
-        <f>VLOOKUP(G27,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L27" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11579,9 +9632,8 @@
       <c r="J28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L28" t="str">
-        <f>VLOOKUP(G28,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L28" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11615,9 +9667,8 @@
       <c r="J29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L29" t="str">
-        <f>VLOOKUP(G29,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L29" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11651,9 +9702,8 @@
       <c r="J30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L30" t="str">
-        <f>VLOOKUP(G30,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L30" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11687,9 +9737,8 @@
       <c r="J31" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L31" t="str">
-        <f>VLOOKUP(G31,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L31" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11723,9 +9772,8 @@
       <c r="J32" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L32" t="str">
-        <f>VLOOKUP(G32,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L32" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11759,9 +9807,8 @@
       <c r="J33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L33" t="str">
-        <f>VLOOKUP(G33,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L33" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11795,9 +9842,8 @@
       <c r="J34" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L34" t="str">
-        <f>VLOOKUP(G34,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L34" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11831,9 +9877,8 @@
       <c r="J35" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L35" t="str">
-        <f>VLOOKUP(G35,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L35" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11867,9 +9912,8 @@
       <c r="J36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L36" t="str">
-        <f>VLOOKUP(G36,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L36" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11903,9 +9947,8 @@
       <c r="J37" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L37" t="str">
-        <f>VLOOKUP(G37,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L37" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11939,9 +9982,8 @@
       <c r="J38" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L38" t="str">
-        <f>VLOOKUP(G38,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L38" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -11975,9 +10017,8 @@
       <c r="J39" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L39" t="str">
-        <f>VLOOKUP(G39,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L39" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12011,9 +10052,8 @@
       <c r="J40" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L40" t="str">
-        <f>VLOOKUP(G40,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L40" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12047,9 +10087,8 @@
       <c r="J41" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L41" t="str">
-        <f>VLOOKUP(G41,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L41" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12083,9 +10122,8 @@
       <c r="J42" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L42" t="str">
-        <f>VLOOKUP(G42,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L42" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12117,11 +10155,10 @@
         <v>0</v>
       </c>
       <c r="J43" s="15" t="s">
-        <v>1614</v>
-      </c>
-      <c r="L43" t="str">
-        <f>VLOOKUP(G43,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+        <v>1596</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12155,9 +10192,8 @@
       <c r="J44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L44" t="str">
-        <f>VLOOKUP(G44,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L44" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12191,9 +10227,8 @@
       <c r="J45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L45" t="str">
-        <f>VLOOKUP(G45,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L45" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12227,9 +10262,8 @@
       <c r="J46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L46" t="str">
-        <f>VLOOKUP(G46,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L46" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12263,9 +10297,8 @@
       <c r="J47" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L47" t="str">
-        <f>VLOOKUP(G47,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L47" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12299,9 +10332,8 @@
       <c r="J48" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L48" t="str">
-        <f>VLOOKUP(G48,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L48" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12335,9 +10367,8 @@
       <c r="J49" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L49" t="str">
-        <f>VLOOKUP(G49,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L49" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12371,9 +10402,8 @@
       <c r="J50" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L50" t="str">
-        <f>VLOOKUP(G50,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L50" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12407,9 +10437,8 @@
       <c r="J51" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L51" t="str">
-        <f>VLOOKUP(G51,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L51" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12443,9 +10472,8 @@
       <c r="J52" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L52" t="str">
-        <f>VLOOKUP(G52,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L52" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12479,9 +10507,8 @@
       <c r="J53" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L53" t="str">
-        <f>VLOOKUP(G53,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L53" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12515,9 +10542,8 @@
       <c r="J54" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L54" t="str">
-        <f>VLOOKUP(G54,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L54" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12551,9 +10577,8 @@
       <c r="J55" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L55" t="str">
-        <f>VLOOKUP(G55,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L55" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12587,9 +10612,8 @@
       <c r="J56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L56" t="str">
-        <f>VLOOKUP(G56,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L56" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12623,9 +10647,8 @@
       <c r="J57" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L57" t="str">
-        <f>VLOOKUP(G57,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L57" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12659,9 +10682,8 @@
       <c r="J58" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L58" t="str">
-        <f>VLOOKUP(G58,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L58" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12695,9 +10717,8 @@
       <c r="J59" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L59" t="str">
-        <f>VLOOKUP(G59,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L59" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12731,9 +10752,8 @@
       <c r="J60" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L60" t="str">
-        <f>VLOOKUP(G60,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L60" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12767,9 +10787,8 @@
       <c r="J61" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L61" t="str">
-        <f>VLOOKUP(G61,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L61" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12803,9 +10822,8 @@
       <c r="J62" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L62" t="str">
-        <f>VLOOKUP(G62,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L62" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12839,9 +10857,8 @@
       <c r="J63" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L63" t="str">
-        <f>VLOOKUP(G63,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L63" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12875,9 +10892,8 @@
       <c r="J64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L64" t="str">
-        <f>VLOOKUP(G64,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L64" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12911,9 +10927,8 @@
       <c r="J65" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L65" t="str">
-        <f>VLOOKUP(G65,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L65" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12947,9 +10962,8 @@
       <c r="J66" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L66" t="str">
-        <f>VLOOKUP(G66,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L66" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -12983,9 +10997,8 @@
       <c r="J67" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L67" t="str">
-        <f>VLOOKUP(G67,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L67" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13019,9 +11032,8 @@
       <c r="J68" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L68" t="str">
-        <f>VLOOKUP(G68,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L68" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13055,9 +11067,8 @@
       <c r="J69" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L69" t="str">
-        <f>VLOOKUP(G69,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L69" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13091,9 +11102,8 @@
       <c r="J70" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L70" t="str">
-        <f>VLOOKUP(G70,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L70" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13127,9 +11137,8 @@
       <c r="J71" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L71" t="str">
-        <f>VLOOKUP(G71,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L71" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13163,9 +11172,8 @@
       <c r="J72" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L72" t="str">
-        <f>VLOOKUP(G72,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L72" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13199,9 +11207,8 @@
       <c r="J73" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L73" t="str">
-        <f>VLOOKUP(G73,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L73" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13235,9 +11242,8 @@
       <c r="J74" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L74" t="str">
-        <f>VLOOKUP(G74,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L74" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13271,9 +11277,8 @@
       <c r="J75" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L75" t="str">
-        <f>VLOOKUP(G75,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L75" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13307,9 +11312,8 @@
       <c r="J76" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L76" t="str">
-        <f>VLOOKUP(G76,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L76" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13343,9 +11347,8 @@
       <c r="J77" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L77" t="str">
-        <f>VLOOKUP(G77,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L77" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13379,9 +11382,8 @@
       <c r="J78" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L78" t="str">
-        <f>VLOOKUP(G78,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L78" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13415,9 +11417,8 @@
       <c r="J79" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L79" t="str">
-        <f>VLOOKUP(G79,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L79" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13451,9 +11452,8 @@
       <c r="J80" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L80" t="str">
-        <f>VLOOKUP(G80,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L80" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13487,9 +11487,8 @@
       <c r="J81" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L81" t="str">
-        <f>VLOOKUP(G81,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L81" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13523,9 +11522,8 @@
       <c r="J82" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L82" t="str">
-        <f>VLOOKUP(G82,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L82" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13559,9 +11557,8 @@
       <c r="J83" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L83" t="str">
-        <f>VLOOKUP(G83,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L83" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13596,7 +11593,7 @@
         <v>70</v>
       </c>
       <c r="L84" t="s">
-        <v>1611</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13630,9 +11627,8 @@
       <c r="J85" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L85" t="str">
-        <f>VLOOKUP(G85,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L85" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13666,9 +11662,8 @@
       <c r="J86" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L86" t="str">
-        <f>VLOOKUP(G86,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L86" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13702,9 +11697,8 @@
       <c r="J87" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L87" t="str">
-        <f>VLOOKUP(G87,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L87" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13738,9 +11732,8 @@
       <c r="J88" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L88" t="str">
-        <f>VLOOKUP(G88,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L88" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13774,9 +11767,8 @@
       <c r="J89" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L89" t="str">
-        <f>VLOOKUP(G89,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L89" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13799,7 +11791,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="14" t="s">
-        <v>1610</v>
+        <v>1593</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>529</v>
@@ -13810,9 +11802,8 @@
       <c r="J90" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L90" t="str">
-        <f>VLOOKUP(G90,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L90" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13846,9 +11837,8 @@
       <c r="J91" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L91" t="str">
-        <f>VLOOKUP(G91,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L91" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13882,9 +11872,8 @@
       <c r="J92" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L92" t="str">
-        <f>VLOOKUP(G92,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L92" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13918,9 +11907,8 @@
       <c r="J93" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L93" t="str">
-        <f>VLOOKUP(G93,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L93" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13954,9 +11942,8 @@
       <c r="J94" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L94" t="str">
-        <f>VLOOKUP(G94,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L94" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -13990,9 +11977,8 @@
       <c r="J95" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L95" t="str">
-        <f>VLOOKUP(G95,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L95" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14026,9 +12012,8 @@
       <c r="J96" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L96" t="str">
-        <f>VLOOKUP(G96,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L96" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14062,9 +12047,8 @@
       <c r="J97" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L97" t="str">
-        <f>VLOOKUP(G97,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L97" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14098,9 +12082,8 @@
       <c r="J98" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L98" t="str">
-        <f>VLOOKUP(G98,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L98" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14134,9 +12117,8 @@
       <c r="J99" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L99" t="str">
-        <f>VLOOKUP(G99,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L99" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14170,9 +12152,8 @@
       <c r="J100" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L100" t="str">
-        <f>VLOOKUP(G100,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L100" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14206,9 +12187,8 @@
       <c r="J101" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L101" t="str">
-        <f>VLOOKUP(G101,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L101" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14242,9 +12222,8 @@
       <c r="J102" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L102" t="str">
-        <f>VLOOKUP(G102,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L102" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14278,9 +12257,8 @@
       <c r="J103" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L103" t="str">
-        <f>VLOOKUP(G103,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L103" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14314,9 +12292,8 @@
       <c r="J104" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L104" t="str">
-        <f>VLOOKUP(G104,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L104" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14350,9 +12327,8 @@
       <c r="J105" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L105" t="str">
-        <f>VLOOKUP(G105,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L105" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14386,9 +12362,8 @@
       <c r="J106" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L106" t="str">
-        <f>VLOOKUP(G106,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L106" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14422,9 +12397,8 @@
       <c r="J107" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L107" t="str">
-        <f>VLOOKUP(G107,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L107" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14458,9 +12432,8 @@
       <c r="J108" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L108" t="str">
-        <f>VLOOKUP(G108,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L108" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14494,9 +12467,8 @@
       <c r="J109" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L109" t="str">
-        <f>VLOOKUP(G109,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L109" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14530,9 +12502,8 @@
       <c r="J110" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L110" t="str">
-        <f>VLOOKUP(G110,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L110" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14566,9 +12537,8 @@
       <c r="J111" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L111" t="str">
-        <f>VLOOKUP(G111,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L111" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14602,9 +12572,8 @@
       <c r="J112" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L112" t="str">
-        <f>VLOOKUP(G112,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L112" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14638,9 +12607,8 @@
       <c r="J113" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L113" t="str">
-        <f>VLOOKUP(G113,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L113" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14674,9 +12642,8 @@
       <c r="J114" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L114" t="str">
-        <f>VLOOKUP(G114,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L114" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14710,9 +12677,8 @@
       <c r="J115" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L115" t="str">
-        <f>VLOOKUP(G115,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L115" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14746,9 +12712,8 @@
       <c r="J116" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L116" t="str">
-        <f>VLOOKUP(G116,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L116" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14782,9 +12747,8 @@
       <c r="J117" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L117" t="str">
-        <f>VLOOKUP(G117,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L117" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14818,9 +12782,8 @@
       <c r="J118" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L118" t="str">
-        <f>VLOOKUP(G118,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L118" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14854,9 +12817,8 @@
       <c r="J119" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L119" t="str">
-        <f>VLOOKUP(G119,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L119" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14890,9 +12852,8 @@
       <c r="J120" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L120" t="str">
-        <f>VLOOKUP(G120,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L120" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14926,9 +12887,8 @@
       <c r="J121" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L121" t="str">
-        <f>VLOOKUP(G121,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L121" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14962,9 +12922,8 @@
       <c r="J122" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L122" t="str">
-        <f>VLOOKUP(G122,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L122" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14998,9 +12957,8 @@
       <c r="J123" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L123" t="str">
-        <f>VLOOKUP(G123,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L123" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15034,9 +12992,8 @@
       <c r="J124" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L124" t="str">
-        <f>VLOOKUP(G124,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L124" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15070,9 +13027,8 @@
       <c r="J125" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L125" t="str">
-        <f>VLOOKUP(G125,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L125" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15106,9 +13062,8 @@
       <c r="J126" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L126" t="str">
-        <f>VLOOKUP(G126,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L126" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15142,9 +13097,8 @@
       <c r="J127" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L127" t="str">
-        <f>VLOOKUP(G127,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L127" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15178,9 +13132,8 @@
       <c r="J128" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L128" t="str">
-        <f>VLOOKUP(G128,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L128" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15214,9 +13167,8 @@
       <c r="J129" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L129" t="str">
-        <f>VLOOKUP(G129,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L129" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15250,9 +13202,8 @@
       <c r="J130" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L130" t="str">
-        <f>VLOOKUP(G130,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L130" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15286,9 +13237,8 @@
       <c r="J131" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L131" t="str">
-        <f>VLOOKUP(G131,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L131" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15322,9 +13272,8 @@
       <c r="J132" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L132" t="str">
-        <f>VLOOKUP(G132,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L132" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15358,9 +13307,8 @@
       <c r="J133" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L133" t="str">
-        <f>VLOOKUP(G133,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L133" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15394,9 +13342,8 @@
       <c r="J134" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L134" t="str">
-        <f>VLOOKUP(G134,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L134" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15430,9 +13377,8 @@
       <c r="J135" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L135" t="str">
-        <f>VLOOKUP(G135,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L135" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15466,9 +13412,8 @@
       <c r="J136" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L136" t="str">
-        <f>VLOOKUP(G136,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L136" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15502,9 +13447,8 @@
       <c r="J137" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L137" t="str">
-        <f>VLOOKUP(G137,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L137" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15538,9 +13482,8 @@
       <c r="J138" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L138" t="str">
-        <f>VLOOKUP(G138,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L138" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15574,9 +13517,8 @@
       <c r="J139" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L139" t="str">
-        <f>VLOOKUP(G139,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L139" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15610,9 +13552,8 @@
       <c r="J140" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L140" t="str">
-        <f>VLOOKUP(G140,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L140" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15646,9 +13587,8 @@
       <c r="J141" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L141" t="str">
-        <f>VLOOKUP(G141,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L141" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15682,9 +13622,8 @@
       <c r="J142" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L142" t="str">
-        <f>VLOOKUP(G142,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L142" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15718,9 +13657,8 @@
       <c r="J143" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L143" t="str">
-        <f>VLOOKUP(G143,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Indeferida</v>
+      <c r="L143" t="s">
+        <v>1600</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15754,9 +13692,8 @@
       <c r="J144" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L144" t="str">
-        <f>VLOOKUP(G144,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L144" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15790,9 +13727,8 @@
       <c r="J145" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L145" t="str">
-        <f>VLOOKUP(G145,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L145" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15826,9 +13762,8 @@
       <c r="J146" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L146" t="str">
-        <f>VLOOKUP(G146,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L146" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15862,9 +13797,8 @@
       <c r="J147" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L147" t="str">
-        <f>VLOOKUP(G147,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L147" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15901,9 +13835,8 @@
       <c r="K148" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="L148" t="str">
-        <f>VLOOKUP(G148,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L148" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15940,9 +13873,8 @@
       <c r="K149" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="L149" t="str">
-        <f>VLOOKUP(G149,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L149" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="150" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -15979,9 +13911,8 @@
       <c r="K150" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="L150" t="str">
-        <f>VLOOKUP(G150,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L150" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16018,9 +13949,8 @@
       <c r="K151" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="L151" t="str">
-        <f>VLOOKUP(G151,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L151" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16057,9 +13987,8 @@
       <c r="K152" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="L152" t="str">
-        <f>VLOOKUP(G152,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L152" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16093,9 +14022,8 @@
       <c r="J153" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L153" t="str">
-        <f>VLOOKUP(G153,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L153" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16129,9 +14057,8 @@
       <c r="J154" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L154" t="str">
-        <f>VLOOKUP(G154,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L154" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="155" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16165,9 +14092,8 @@
       <c r="J155" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L155" t="str">
-        <f>VLOOKUP(G155,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Não Compareceu</v>
+      <c r="L155" t="s">
+        <v>1599</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16201,9 +14127,8 @@
       <c r="J156" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="L156" t="str">
-        <f>VLOOKUP(G156,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L156" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16240,9 +14165,8 @@
       <c r="K157" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="L157" t="str">
-        <f>VLOOKUP(G157,[1]Planilha1!$E$2:$I$175,5,0)</f>
-        <v>Matrícula Deferida</v>
+      <c r="L157" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16264,11 +14188,11 @@
       <c r="F158">
         <v>10</v>
       </c>
-      <c r="G158" t="s">
+      <c r="G158" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H158" t="s">
         <v>1571</v>
-      </c>
-      <c r="H158" t="s">
-        <v>1572</v>
       </c>
       <c r="I158" s="3">
         <v>0</v>
@@ -16276,8 +14200,8 @@
       <c r="J158" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L158" t="s">
-        <v>1612</v>
+      <c r="L158" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16299,11 +14223,11 @@
       <c r="F159">
         <v>11</v>
       </c>
-      <c r="G159" t="s">
-        <v>1573</v>
+      <c r="G159" s="19" t="s">
+        <v>90</v>
       </c>
       <c r="H159" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="I159" s="4">
         <v>0</v>
@@ -16312,8 +14236,8 @@
         <v>50</v>
       </c>
       <c r="K159" s="4"/>
-      <c r="L159" t="s">
-        <v>1612</v>
+      <c r="L159" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16335,21 +14259,21 @@
       <c r="F160">
         <v>12</v>
       </c>
-      <c r="G160" t="s">
-        <v>1575</v>
+      <c r="G160" s="19" t="s">
+        <v>95</v>
       </c>
       <c r="H160" t="s">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="I160" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K160" s="4"/>
       <c r="L160" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16371,21 +14295,21 @@
       <c r="F161">
         <v>8</v>
       </c>
-      <c r="G161" t="s">
-        <v>1577</v>
+      <c r="G161" s="19" t="s">
+        <v>573</v>
       </c>
       <c r="H161" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="I161" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K161" s="4"/>
       <c r="L161" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16407,11 +14331,11 @@
       <c r="F162">
         <v>9</v>
       </c>
-      <c r="G162" t="s">
-        <v>1579</v>
+      <c r="G162" s="19" t="s">
+        <v>595</v>
       </c>
       <c r="H162" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="I162" s="4">
         <v>0</v>
@@ -16420,8 +14344,8 @@
         <v>50</v>
       </c>
       <c r="K162" s="4"/>
-      <c r="L162" t="s">
-        <v>1612</v>
+      <c r="L162" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16443,21 +14367,21 @@
       <c r="F163">
         <v>10</v>
       </c>
-      <c r="G163" t="s">
-        <v>1581</v>
+      <c r="G163" s="19" t="s">
+        <v>638</v>
       </c>
       <c r="H163" t="s">
-        <v>1582</v>
+        <v>1576</v>
       </c>
       <c r="I163" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K163" s="4"/>
       <c r="L163" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16480,20 +14404,20 @@
         <v>11</v>
       </c>
       <c r="G164" t="s">
-        <v>1583</v>
+        <v>1577</v>
       </c>
       <c r="H164" t="s">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="I164" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K164" s="4"/>
       <c r="L164" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16515,11 +14439,11 @@
       <c r="F165">
         <v>2</v>
       </c>
-      <c r="G165" t="s">
-        <v>1585</v>
+      <c r="G165" s="19" t="s">
+        <v>482</v>
       </c>
       <c r="H165" t="s">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="I165" s="4">
         <v>0</v>
@@ -16528,8 +14452,8 @@
         <v>50</v>
       </c>
       <c r="K165" s="4"/>
-      <c r="L165" t="s">
-        <v>1612</v>
+      <c r="L165" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16551,21 +14475,21 @@
       <c r="F166">
         <v>9</v>
       </c>
-      <c r="G166" t="s">
-        <v>1587</v>
+      <c r="G166" s="19" t="s">
+        <v>1188</v>
       </c>
       <c r="H166" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="I166" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K166" s="4"/>
       <c r="L166" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16587,11 +14511,11 @@
       <c r="F167">
         <v>4</v>
       </c>
-      <c r="G167" t="s">
-        <v>1589</v>
+      <c r="G167" s="19" t="s">
+        <v>1272</v>
       </c>
       <c r="H167" t="s">
-        <v>1590</v>
+        <v>1581</v>
       </c>
       <c r="I167" s="4">
         <v>0</v>
@@ -16600,10 +14524,10 @@
         <v>50</v>
       </c>
       <c r="K167" t="s">
-        <v>1591</v>
-      </c>
-      <c r="L167" t="s">
-        <v>1612</v>
+        <v>1582</v>
+      </c>
+      <c r="L167" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16625,21 +14549,21 @@
       <c r="F168">
         <v>4</v>
       </c>
-      <c r="G168" t="s">
-        <v>1592</v>
+      <c r="G168" s="19" t="s">
+        <v>1564</v>
       </c>
       <c r="H168" t="s">
-        <v>1593</v>
+        <v>1583</v>
       </c>
       <c r="I168" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K168" s="4"/>
       <c r="L168" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16661,11 +14585,11 @@
       <c r="F169">
         <v>3</v>
       </c>
-      <c r="G169" t="s">
-        <v>1594</v>
+      <c r="G169" s="19" t="s">
+        <v>1401</v>
       </c>
       <c r="H169" t="s">
-        <v>1595</v>
+        <v>1584</v>
       </c>
       <c r="I169" s="4">
         <v>0</v>
@@ -16674,8 +14598,8 @@
         <v>50</v>
       </c>
       <c r="K169" s="4"/>
-      <c r="L169" t="s">
-        <v>1612</v>
+      <c r="L169" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16697,11 +14621,11 @@
       <c r="F170">
         <v>3</v>
       </c>
-      <c r="G170" t="s">
-        <v>1596</v>
+      <c r="G170" s="19" t="s">
+        <v>1207</v>
       </c>
       <c r="H170" t="s">
-        <v>1597</v>
+        <v>1585</v>
       </c>
       <c r="I170" s="4">
         <v>0</v>
@@ -16710,8 +14634,8 @@
         <v>50</v>
       </c>
       <c r="K170" s="4"/>
-      <c r="L170" t="s">
-        <v>1612</v>
+      <c r="L170" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16733,11 +14657,11 @@
       <c r="F171">
         <v>4</v>
       </c>
-      <c r="G171" t="s">
-        <v>1598</v>
+      <c r="G171" s="19" t="s">
+        <v>1130</v>
       </c>
       <c r="H171" t="s">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="I171" s="4">
         <v>0</v>
@@ -16746,8 +14670,8 @@
         <v>50</v>
       </c>
       <c r="K171" s="4"/>
-      <c r="L171" t="s">
-        <v>1612</v>
+      <c r="L171" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16769,23 +14693,23 @@
       <c r="F172">
         <v>10</v>
       </c>
-      <c r="G172" t="s">
-        <v>1600</v>
+      <c r="G172" s="19" t="s">
+        <v>1166</v>
       </c>
       <c r="H172" t="s">
-        <v>1601</v>
+        <v>1587</v>
       </c>
       <c r="I172" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K172" t="s">
         <v>789</v>
       </c>
       <c r="L172" t="s">
-        <v>1612</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="173" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16807,11 +14731,11 @@
       <c r="F173">
         <v>7</v>
       </c>
-      <c r="G173" t="s">
-        <v>1602</v>
+      <c r="G173" s="19" t="s">
+        <v>1161</v>
       </c>
       <c r="H173" t="s">
-        <v>1603</v>
+        <v>1588</v>
       </c>
       <c r="I173" s="4">
         <v>0</v>
@@ -16822,8 +14746,8 @@
       <c r="K173" t="s">
         <v>789</v>
       </c>
-      <c r="L173" t="s">
-        <v>1612</v>
+      <c r="L173" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16845,11 +14769,11 @@
       <c r="F174">
         <v>5</v>
       </c>
-      <c r="G174" t="s">
-        <v>1604</v>
+      <c r="G174" s="19" t="s">
+        <v>1157</v>
       </c>
       <c r="H174" t="s">
-        <v>1605</v>
+        <v>1589</v>
       </c>
       <c r="I174" s="4">
         <v>0</v>
@@ -16860,8 +14784,8 @@
       <c r="K174" t="s">
         <v>789</v>
       </c>
-      <c r="L174" t="s">
-        <v>1612</v>
+      <c r="L174" s="19" t="s">
+        <v>1602</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -16883,11 +14807,11 @@
       <c r="F175">
         <v>2</v>
       </c>
-      <c r="G175" t="s">
-        <v>1606</v>
+      <c r="G175" s="19" t="s">
+        <v>1149</v>
       </c>
       <c r="H175" t="s">
-        <v>1607</v>
+        <v>1590</v>
       </c>
       <c r="I175" s="4">
         <v>0</v>
@@ -16898,13 +14822,413 @@
       <c r="K175" t="s">
         <v>789</v>
       </c>
-      <c r="L175" t="s">
-        <v>1612</v>
+      <c r="L175" s="19" t="s">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" t="s">
+        <v>22</v>
+      </c>
+      <c r="D176" t="s">
+        <v>24</v>
+      </c>
+      <c r="E176" t="s">
+        <v>25</v>
+      </c>
+      <c r="F176">
+        <v>5</v>
+      </c>
+      <c r="G176" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H176" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I176" s="4">
+        <v>0</v>
+      </c>
+      <c r="J176" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L176" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C177" t="s">
+        <v>22</v>
+      </c>
+      <c r="D177" t="s">
+        <v>24</v>
+      </c>
+      <c r="E177" t="s">
+        <v>51</v>
+      </c>
+      <c r="F177">
+        <v>6</v>
+      </c>
+      <c r="G177" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H177" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I177" s="4">
+        <v>0</v>
+      </c>
+      <c r="J177" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K177" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L177" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C178" t="s">
+        <v>22</v>
+      </c>
+      <c r="D178" t="s">
+        <v>24</v>
+      </c>
+      <c r="E178" t="s">
+        <v>54</v>
+      </c>
+      <c r="F178">
+        <v>11</v>
+      </c>
+      <c r="G178" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H178" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I178" s="4">
+        <v>0</v>
+      </c>
+      <c r="J178" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K178" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="L178" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" t="s">
+        <v>22</v>
+      </c>
+      <c r="D179" t="s">
+        <v>24</v>
+      </c>
+      <c r="E179" t="s">
+        <v>41</v>
+      </c>
+      <c r="F179">
+        <v>7</v>
+      </c>
+      <c r="G179" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H179" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I179" s="4">
+        <v>0</v>
+      </c>
+      <c r="J179" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K179" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L179" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B180" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C180" t="s">
+        <v>29</v>
+      </c>
+      <c r="D180" t="s">
+        <v>31</v>
+      </c>
+      <c r="E180" t="s">
+        <v>25</v>
+      </c>
+      <c r="F180">
+        <v>13</v>
+      </c>
+      <c r="G180" t="s">
+        <v>100</v>
+      </c>
+      <c r="H180" t="s">
+        <v>101</v>
+      </c>
+      <c r="I180" s="4">
+        <v>0</v>
+      </c>
+      <c r="J180" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L180" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B181" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C181" t="s">
+        <v>29</v>
+      </c>
+      <c r="D181" t="s">
+        <v>31</v>
+      </c>
+      <c r="E181" t="s">
+        <v>59</v>
+      </c>
+      <c r="F181">
+        <v>4</v>
+      </c>
+      <c r="G181" t="s">
+        <v>605</v>
+      </c>
+      <c r="H181" t="s">
+        <v>606</v>
+      </c>
+      <c r="I181" s="4">
+        <v>0</v>
+      </c>
+      <c r="J181" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L181" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B182" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" t="s">
+        <v>29</v>
+      </c>
+      <c r="D182" t="s">
+        <v>31</v>
+      </c>
+      <c r="E182" t="s">
+        <v>37</v>
+      </c>
+      <c r="F182">
+        <v>12</v>
+      </c>
+      <c r="G182" t="s">
+        <v>650</v>
+      </c>
+      <c r="H182" t="s">
+        <v>651</v>
+      </c>
+      <c r="I182" s="4">
+        <v>0</v>
+      </c>
+      <c r="J182" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L182" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B183" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="C183" t="s">
+        <v>29</v>
+      </c>
+      <c r="D183" t="s">
+        <v>31</v>
+      </c>
+      <c r="E183" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F183">
+        <v>14</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I183" s="4">
+        <v>0</v>
+      </c>
+      <c r="J183" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L183" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B184" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C184" t="s">
+        <v>210</v>
+      </c>
+      <c r="D184" t="s">
+        <v>108</v>
+      </c>
+      <c r="E184" t="s">
+        <v>65</v>
+      </c>
+      <c r="F184">
+        <v>3</v>
+      </c>
+      <c r="G184" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H184" t="s">
+        <v>1217</v>
+      </c>
+      <c r="I184" s="4">
+        <v>0</v>
+      </c>
+      <c r="J184" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="L184" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B185" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C185" t="s">
+        <v>210</v>
+      </c>
+      <c r="D185" t="s">
+        <v>108</v>
+      </c>
+      <c r="E185" t="s">
+        <v>59</v>
+      </c>
+      <c r="F185">
+        <v>5</v>
+      </c>
+      <c r="G185" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H185" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I185" s="4">
+        <v>0</v>
+      </c>
+      <c r="J185" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K185" s="19" t="s">
+        <v>1582</v>
+      </c>
+      <c r="L185" s="18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="19" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B186" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C186" t="s">
+        <v>210</v>
+      </c>
+      <c r="D186" t="s">
+        <v>108</v>
+      </c>
+      <c r="E186" t="s">
+        <v>41</v>
+      </c>
+      <c r="F186">
+        <v>6</v>
+      </c>
+      <c r="G186" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H186" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I186" s="4">
+        <v>0</v>
+      </c>
+      <c r="J186" s="19" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K186" s="19" t="s">
+        <v>1582</v>
+      </c>
+      <c r="L186" s="18" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L175" xr:uid="{DCF350D5-A937-4A0D-B6AA-DEB16DD30D95}"/>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <autoFilter ref="A1:L186" xr:uid="{DCF350D5-A937-4A0D-B6AA-DEB16DD30D95}"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -16918,6 +15242,7 @@
   <dimension ref="A1:N1121"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
     <col min="10" max="11" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17404,7 +15729,7 @@
         <v>87</v>
       </c>
       <c r="L11" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>36</v>
@@ -17449,7 +15774,7 @@
         <v>94</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M12" s="11" t="s">
         <v>36</v>
@@ -17494,7 +15819,7 @@
         <v>98</v>
       </c>
       <c r="L13" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M13" s="11" t="s">
         <v>36</v>
@@ -17538,14 +15863,14 @@
       <c r="K14" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>88</v>
+      <c r="L14" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -17583,14 +15908,14 @@
       <c r="K15" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L15" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>88</v>
+      <c r="L15" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M15" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -21094,7 +19419,7 @@
         <v>484</v>
       </c>
       <c r="L93" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M93" s="11" t="s">
         <v>36</v>
@@ -21949,7 +20274,7 @@
         <v>576</v>
       </c>
       <c r="L112" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M112" s="11" t="s">
         <v>36</v>
@@ -22129,7 +20454,7 @@
         <v>599</v>
       </c>
       <c r="L116" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M116" s="11" t="s">
         <v>36</v>
@@ -22218,14 +20543,14 @@
       <c r="K118" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="L118" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N118" s="5" t="s">
-        <v>88</v>
+      <c r="L118" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M118" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="119" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -22624,7 +20949,7 @@
         <v>640</v>
       </c>
       <c r="L127" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M127" s="11" t="s">
         <v>36</v>
@@ -22714,7 +21039,7 @@
         <v>646</v>
       </c>
       <c r="L129" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M129" s="11" t="s">
         <v>36</v>
@@ -22803,14 +21128,14 @@
       <c r="K131" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="L131" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M131" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N131" s="5" t="s">
-        <v>88</v>
+      <c r="L131" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M131" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N131" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="132" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -29643,7 +27968,7 @@
         <v>576</v>
       </c>
       <c r="L283" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M283" s="11" t="s">
         <v>36</v>
@@ -29688,7 +28013,7 @@
         <v>599</v>
       </c>
       <c r="L284" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M284" s="11" t="s">
         <v>36</v>
@@ -29778,7 +28103,7 @@
         <v>640</v>
       </c>
       <c r="L286" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M286" s="11" t="s">
         <v>36</v>
@@ -29868,7 +28193,7 @@
         <v>646</v>
       </c>
       <c r="L288" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M288" s="11" t="s">
         <v>36</v>
@@ -29912,14 +28237,14 @@
       <c r="K289" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="L289" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M289" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N289" s="5" t="s">
-        <v>88</v>
+      <c r="L289" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M289" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N289" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="290" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -33872,7 +32197,7 @@
         <v>484</v>
       </c>
       <c r="L377" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M377" s="11" t="s">
         <v>36</v>
@@ -34457,7 +32782,7 @@
         <v>576</v>
       </c>
       <c r="L390" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M390" s="11" t="s">
         <v>36</v>
@@ -34502,7 +32827,7 @@
         <v>599</v>
       </c>
       <c r="L391" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M391" s="11" t="s">
         <v>36</v>
@@ -34591,14 +32916,14 @@
       <c r="K393" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="L393" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M393" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N393" s="5" t="s">
-        <v>88</v>
+      <c r="L393" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M393" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N393" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="394" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -34772,7 +33097,7 @@
         <v>640</v>
       </c>
       <c r="L397" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M397" s="11" t="s">
         <v>36</v>
@@ -34862,7 +33187,7 @@
         <v>646</v>
       </c>
       <c r="L399" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M399" s="11" t="s">
         <v>36</v>
@@ -34951,14 +33276,14 @@
       <c r="K401" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="L401" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M401" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N401" s="5" t="s">
-        <v>88</v>
+      <c r="L401" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M401" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N401" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="402" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -40440,7 +38765,7 @@
         <v>484</v>
       </c>
       <c r="L523" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M523" s="11" t="s">
         <v>36</v>
@@ -40529,14 +38854,14 @@
       <c r="K525" s="1" t="s">
         <v>609</v>
       </c>
-      <c r="L525" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M525" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N525" s="5" t="s">
-        <v>88</v>
+      <c r="L525" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M525" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N525" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="526" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -41879,7 +40204,7 @@
         <v>576</v>
       </c>
       <c r="L555" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M555" s="11" t="s">
         <v>36</v>
@@ -41924,7 +40249,7 @@
         <v>599</v>
       </c>
       <c r="L556" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M556" s="11" t="s">
         <v>36</v>
@@ -41969,7 +40294,7 @@
         <v>640</v>
       </c>
       <c r="L557" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M557" s="11" t="s">
         <v>36</v>
@@ -42014,7 +40339,7 @@
         <v>646</v>
       </c>
       <c r="L558" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M558" s="11" t="s">
         <v>36</v>
@@ -42058,14 +40383,14 @@
       <c r="K559" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="L559" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M559" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N559" s="5" t="s">
-        <v>88</v>
+      <c r="L559" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M559" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N559" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="560" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -44398,7 +42723,7 @@
         <v>576</v>
       </c>
       <c r="L611" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M611" s="11" t="s">
         <v>36</v>
@@ -44443,7 +42768,7 @@
         <v>599</v>
       </c>
       <c r="L612" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M612" s="11" t="s">
         <v>36</v>
@@ -44533,7 +42858,7 @@
         <v>640</v>
       </c>
       <c r="L614" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M614" s="11" t="s">
         <v>36</v>
@@ -44578,7 +42903,7 @@
         <v>646</v>
       </c>
       <c r="L615" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M615" s="11" t="s">
         <v>36</v>
@@ -44667,14 +42992,14 @@
       <c r="K617" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="L617" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M617" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N617" s="5" t="s">
-        <v>88</v>
+      <c r="L617" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M617" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="N617" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="618" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -47319,7 +45644,7 @@
         <v>1132</v>
       </c>
       <c r="L676" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M676" s="11" t="s">
         <v>36</v>
@@ -47363,14 +45688,14 @@
       <c r="K677" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="L677" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M677" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N677" s="5" t="s">
-        <v>88</v>
+      <c r="L677" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M677" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N677" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="678" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -47408,14 +45733,14 @@
       <c r="K678" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="L678" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M678" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N678" s="5" t="s">
-        <v>88</v>
+      <c r="L678" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M678" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N678" s="18" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="679" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -47453,14 +45778,14 @@
       <c r="K679" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="L679" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M679" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N679" s="5" t="s">
-        <v>88</v>
+      <c r="L679" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M679" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N679" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="680" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -47634,7 +45959,7 @@
         <v>1151</v>
       </c>
       <c r="L683" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M683" s="11" t="s">
         <v>36</v>
@@ -47814,7 +46139,7 @@
         <v>1159</v>
       </c>
       <c r="L687" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M687" s="11" t="s">
         <v>36</v>
@@ -47904,7 +46229,7 @@
         <v>1163</v>
       </c>
       <c r="L689" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M689" s="11" t="s">
         <v>36</v>
@@ -48039,7 +46364,7 @@
         <v>1168</v>
       </c>
       <c r="L692" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M692" s="11" t="s">
         <v>36</v>
@@ -48128,14 +46453,14 @@
       <c r="K694" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="L694" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M694" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N694" s="5" t="s">
-        <v>88</v>
+      <c r="L694" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M694" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N694" s="18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="695" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -48757,7 +47082,7 @@
         <v>1151</v>
       </c>
       <c r="L708" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M708" s="11" t="s">
         <v>36</v>
@@ -48892,7 +47217,7 @@
         <v>1159</v>
       </c>
       <c r="L711" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M711" s="11" t="s">
         <v>36</v>
@@ -48982,7 +47307,7 @@
         <v>1163</v>
       </c>
       <c r="L713" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M713" s="11" t="s">
         <v>36</v>
@@ -49117,7 +47442,7 @@
         <v>1168</v>
       </c>
       <c r="L716" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M716" s="11" t="s">
         <v>36</v>
@@ -49161,14 +47486,14 @@
       <c r="K717" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="L717" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M717" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N717" s="5" t="s">
-        <v>88</v>
+      <c r="L717" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M717" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N717" s="18" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="718" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -50054,7 +48379,7 @@
         <v>1190</v>
       </c>
       <c r="L737" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M737" s="11" t="s">
         <v>36</v>
@@ -50369,7 +48694,7 @@
         <v>1209</v>
       </c>
       <c r="L744" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M744" s="11" t="s">
         <v>36</v>
@@ -50503,14 +48828,14 @@
       <c r="K747" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="L747" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M747" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N747" s="5" t="s">
-        <v>88</v>
+      <c r="L747" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M747" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N747" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="748" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -51494,7 +49819,7 @@
         <v>1274</v>
       </c>
       <c r="L769" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M769" s="11" t="s">
         <v>36</v>
@@ -51538,14 +49863,14 @@
       <c r="K770" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="L770" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M770" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N770" s="5" t="s">
-        <v>88</v>
+      <c r="L770" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M770" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N770" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="771" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -51853,14 +50178,14 @@
       <c r="K777" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="L777" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M777" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N777" s="5" t="s">
-        <v>88</v>
+      <c r="L777" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M777" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N777" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="778" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -53429,7 +51754,7 @@
         <v>1403</v>
       </c>
       <c r="L812" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M812" s="11" t="s">
         <v>36</v>
@@ -55904,7 +54229,7 @@
         <v>1566</v>
       </c>
       <c r="L867" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M867" s="11" t="s">
         <v>36</v>
@@ -56038,7 +54363,7 @@
         <v>1209</v>
       </c>
       <c r="L870" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M870" s="11" t="s">
         <v>36</v>
@@ -56082,14 +54407,14 @@
       <c r="K871" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="L871" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M871" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N871" s="5" t="s">
-        <v>88</v>
+      <c r="L871" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M871" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N871" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="872" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -56578,7 +54903,7 @@
         <v>1274</v>
       </c>
       <c r="L882" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M882" s="11" t="s">
         <v>36</v>
@@ -56622,14 +54947,14 @@
       <c r="K883" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="L883" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M883" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N883" s="5" t="s">
-        <v>88</v>
+      <c r="L883" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M883" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N883" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="884" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -56757,14 +55082,14 @@
       <c r="K886" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="L886" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M886" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N886" s="5" t="s">
-        <v>88</v>
+      <c r="L886" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M886" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N886" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="887" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -57478,7 +55803,7 @@
         <v>1403</v>
       </c>
       <c r="L902" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M902" s="11" t="s">
         <v>36</v>
@@ -58783,7 +57108,7 @@
         <v>1566</v>
       </c>
       <c r="L931" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M931" s="11" t="s">
         <v>36</v>
@@ -58962,7 +57287,7 @@
         <v>1209</v>
       </c>
       <c r="L935" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M935" s="11" t="s">
         <v>36</v>
@@ -59006,14 +57331,14 @@
       <c r="K936" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="L936" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M936" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N936" s="5" t="s">
-        <v>88</v>
+      <c r="L936" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M936" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N936" s="18" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="937" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -59682,7 +58007,7 @@
         <v>1274</v>
       </c>
       <c r="L951" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M951" s="11" t="s">
         <v>36</v>
@@ -59726,14 +58051,14 @@
       <c r="K952" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="L952" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M952" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N952" s="5" t="s">
-        <v>88</v>
+      <c r="L952" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M952" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N952" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="953" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -59951,14 +58276,14 @@
       <c r="K957" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="L957" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M957" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N957" s="5" t="s">
-        <v>88</v>
+      <c r="L957" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M957" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N957" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="958" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -61212,7 +59537,7 @@
         <v>1403</v>
       </c>
       <c r="L985" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M985" s="11" t="s">
         <v>36</v>
@@ -63147,7 +61472,7 @@
         <v>1566</v>
       </c>
       <c r="L1028" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1028" s="11" t="s">
         <v>36</v>
@@ -63324,7 +61649,7 @@
         <v>1403</v>
       </c>
       <c r="L1032" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1032" s="11" t="s">
         <v>36</v>
@@ -63368,7 +61693,7 @@
         <v>1566</v>
       </c>
       <c r="L1033" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1033" s="11" t="s">
         <v>36</v>
@@ -63500,7 +61825,7 @@
         <v>1403</v>
       </c>
       <c r="L1036" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1036" s="11" t="s">
         <v>36</v>
@@ -63544,7 +61869,7 @@
         <v>1566</v>
       </c>
       <c r="L1037" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1037" s="11" t="s">
         <v>36</v>
@@ -63723,7 +62048,7 @@
         <v>1274</v>
       </c>
       <c r="L1041" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1041" s="11" t="s">
         <v>36</v>
@@ -63767,14 +62092,14 @@
       <c r="K1042" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="L1042" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1042" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1042" s="5" t="s">
-        <v>88</v>
+      <c r="L1042" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M1042" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1042" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="1043" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -63812,14 +62137,14 @@
       <c r="K1043" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="L1043" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1043" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1043" s="5" t="s">
-        <v>88</v>
+      <c r="L1043" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M1043" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1043" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="1044" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -65162,7 +63487,7 @@
         <v>1274</v>
       </c>
       <c r="L1073" s="12" t="s">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="M1073" s="11" t="s">
         <v>36</v>
@@ -65206,14 +63531,14 @@
       <c r="K1074" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="L1074" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1074" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1074" s="5" t="s">
-        <v>88</v>
+      <c r="L1074" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M1074" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1074" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="1075" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">
@@ -65296,14 +63621,14 @@
       <c r="K1076" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="L1076" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="M1076" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="N1076" s="5" t="s">
-        <v>88</v>
+      <c r="L1076" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="M1076" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="N1076" s="18" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="1077" spans="1:14" ht="14.4" x14ac:dyDescent="0.3">

--- a/public/Dados_copese.xlsx
+++ b/public/Dados_copese.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leonardo\sisu-ufpi-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2693AA-4DE2-44BA-865D-A72BF59D9C7B}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4BAAB1F-4D10-40ED-9301-CB51D52F844A}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="vagas" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14418" uniqueCount="1603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14418" uniqueCount="1602">
   <si>
     <t>ano_s</t>
   </si>
@@ -4837,9 +4837,6 @@
   </si>
   <si>
     <t>Matrícula Indeferida</t>
-  </si>
-  <si>
-    <t>Aguardando matrícula</t>
   </si>
   <si>
     <t>ND</t>
@@ -4849,11 +4846,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4939,32 +4943,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -7370,11 +7375,11 @@
   convocacoes!E:E, F60,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I60" s="2">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7442,11 +7447,11 @@
   convocacoes!E:E, F62,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7478,11 +7483,11 @@
   convocacoes!E:E, F63,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7514,11 +7519,11 @@
   convocacoes!E:E, F64,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7550,11 +7555,11 @@
   convocacoes!E:E, F65,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7622,11 +7627,11 @@
   convocacoes!E:E, F67,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7694,11 +7699,11 @@
   convocacoes!E:E, F69,
   convocacoes!I:I, 1
 )</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="2">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -8628,7 +8633,7 @@
     <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <autoFilter ref="A1:I59" xr:uid="{757EA66F-DC97-48A0-A498-5FBE3B3AA156}"/>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -14201,7 +14206,7 @@
         <v>50</v>
       </c>
       <c r="L158" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14237,7 +14242,7 @@
       </c>
       <c r="K159" s="4"/>
       <c r="L159" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14345,7 +14350,7 @@
       </c>
       <c r="K162" s="4"/>
       <c r="L162" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14453,7 +14458,7 @@
       </c>
       <c r="K165" s="4"/>
       <c r="L165" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14527,7 +14532,7 @@
         <v>1582</v>
       </c>
       <c r="L167" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14599,7 +14604,7 @@
       </c>
       <c r="K169" s="4"/>
       <c r="L169" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14635,7 +14640,7 @@
       </c>
       <c r="K170" s="4"/>
       <c r="L170" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14671,7 +14676,7 @@
       </c>
       <c r="K171" s="4"/>
       <c r="L171" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14747,7 +14752,7 @@
         <v>789</v>
       </c>
       <c r="L173" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14785,7 +14790,7 @@
         <v>789</v>
       </c>
       <c r="L174" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -14823,7 +14828,7 @@
         <v>789</v>
       </c>
       <c r="L175" s="19" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -14854,8 +14859,8 @@
       <c r="I176" s="4">
         <v>0</v>
       </c>
-      <c r="J176" s="19" t="s">
-        <v>1601</v>
+      <c r="J176" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="L176" s="18" t="s">
         <v>88</v>
@@ -14887,10 +14892,10 @@
         <v>1137</v>
       </c>
       <c r="I177" s="4">
-        <v>0</v>
-      </c>
-      <c r="J177" s="19" t="s">
-        <v>1601</v>
+        <v>1</v>
+      </c>
+      <c r="J177" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="K177" s="19" t="s">
         <v>25</v>
@@ -14927,8 +14932,8 @@
       <c r="I178" s="4">
         <v>0</v>
       </c>
-      <c r="J178" s="19" t="s">
-        <v>1601</v>
+      <c r="J178" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="K178" s="19" t="s">
         <v>789</v>
@@ -14963,10 +14968,10 @@
         <v>1140</v>
       </c>
       <c r="I179" s="4">
-        <v>0</v>
-      </c>
-      <c r="J179" s="19" t="s">
-        <v>1601</v>
+        <v>1</v>
+      </c>
+      <c r="J179" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="K179" s="19" t="s">
         <v>25</v>
@@ -15001,13 +15006,13 @@
         <v>101</v>
       </c>
       <c r="I180" s="4">
-        <v>0</v>
-      </c>
-      <c r="J180" s="19" t="s">
-        <v>1601</v>
-      </c>
-      <c r="L180" s="18" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L180" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15038,8 +15043,8 @@
       <c r="I181" s="4">
         <v>0</v>
       </c>
-      <c r="J181" s="19" t="s">
-        <v>1601</v>
+      <c r="J181" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="L181" s="18" t="s">
         <v>88</v>
@@ -15071,13 +15076,13 @@
         <v>651</v>
       </c>
       <c r="I182" s="4">
-        <v>0</v>
-      </c>
-      <c r="J182" s="19" t="s">
-        <v>1601</v>
-      </c>
-      <c r="L182" s="18" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L182" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15106,13 +15111,13 @@
         <v>107</v>
       </c>
       <c r="I183" s="4">
-        <v>0</v>
-      </c>
-      <c r="J183" s="19" t="s">
-        <v>1601</v>
-      </c>
-      <c r="L183" s="18" t="s">
-        <v>88</v>
+        <v>1</v>
+      </c>
+      <c r="J183" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L183" t="s">
+        <v>1594</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -15141,10 +15146,10 @@
         <v>1217</v>
       </c>
       <c r="I184" s="4">
-        <v>0</v>
-      </c>
-      <c r="J184" s="19" t="s">
-        <v>1601</v>
+        <v>1</v>
+      </c>
+      <c r="J184" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="L184" s="18" t="s">
         <v>88</v>
@@ -15176,10 +15181,10 @@
         <v>1276</v>
       </c>
       <c r="I185" s="4">
-        <v>0</v>
-      </c>
-      <c r="J185" s="19" t="s">
-        <v>1601</v>
+        <v>1</v>
+      </c>
+      <c r="J185" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="K185" s="19" t="s">
         <v>1582</v>
@@ -15214,10 +15219,10 @@
         <v>1297</v>
       </c>
       <c r="I186" s="4">
-        <v>0</v>
-      </c>
-      <c r="J186" s="19" t="s">
-        <v>1601</v>
+        <v>1</v>
+      </c>
+      <c r="J186" s="20" t="s">
+        <v>70</v>
       </c>
       <c r="K186" s="19" t="s">
         <v>1582</v>
@@ -15228,7 +15233,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L186" xr:uid="{DCF350D5-A937-4A0D-B6AA-DEB16DD30D95}"/>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
